--- a/artfynd/A 13365-2024 artfynd.xlsx
+++ b/artfynd/A 13365-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116915342</v>
+        <v>116915393</v>
       </c>
       <c r="B2" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459297</v>
+        <v>459192</v>
       </c>
       <c r="R2" t="n">
-        <v>6507581</v>
+        <v>6507451</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,17 +760,13 @@
           <t>2024-05-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spelspillning</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116915343</v>
+        <v>116915339</v>
       </c>
       <c r="B3" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459316</v>
+        <v>459269</v>
       </c>
       <c r="R3" t="n">
-        <v>6507539</v>
+        <v>6507641</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -913,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116915339</v>
+        <v>116915340</v>
       </c>
       <c r="B4" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459269</v>
+        <v>459288</v>
       </c>
       <c r="R4" t="n">
-        <v>6507641</v>
+        <v>6507622</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116915351</v>
+        <v>116915342</v>
       </c>
       <c r="B5" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459219</v>
+        <v>459297</v>
       </c>
       <c r="R5" t="n">
-        <v>6507513</v>
+        <v>6507581</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1151,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116915391</v>
+        <v>116915343</v>
       </c>
       <c r="B6" t="n">
-        <v>104867</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,35 +1142,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459207</v>
+        <v>459316</v>
       </c>
       <c r="R6" t="n">
-        <v>6507444</v>
+        <v>6507539</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1241,13 +1212,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spelspillning</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,12 +1248,7 @@
         <v>116915346</v>
       </c>
       <c r="B7" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,12 +1362,7 @@
         <v>116915347</v>
       </c>
       <c r="B8" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,12 +1476,7 @@
         <v>116915348</v>
       </c>
       <c r="B9" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,15 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116915387</v>
+        <v>116915349</v>
       </c>
       <c r="B10" t="n">
-        <v>104867</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,35 +1598,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1682,7 +1633,7 @@
         <v>459224</v>
       </c>
       <c r="R10" t="n">
-        <v>6507509</v>
+        <v>6507515</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1717,13 +1668,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spelspillning</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,15 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116915353</v>
+        <v>116915351</v>
       </c>
       <c r="B11" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459212</v>
+        <v>459219</v>
       </c>
       <c r="R11" t="n">
-        <v>6507476</v>
+        <v>6507513</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1865,15 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116915340</v>
+        <v>116915353</v>
       </c>
       <c r="B12" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459288</v>
+        <v>459212</v>
       </c>
       <c r="R12" t="n">
-        <v>6507622</v>
+        <v>6507476</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1984,15 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116915349</v>
+        <v>116915354</v>
       </c>
       <c r="B13" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459224</v>
+        <v>459205</v>
       </c>
       <c r="R13" t="n">
-        <v>6507515</v>
+        <v>6507420</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2103,15 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116915393</v>
+        <v>116915356</v>
       </c>
       <c r="B14" t="n">
-        <v>104867</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,35 +2054,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2155,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459192</v>
+        <v>459222</v>
       </c>
       <c r="R14" t="n">
-        <v>6507451</v>
+        <v>6507417</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2193,13 +2124,17 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>spelspillning</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2215,6 +2150,234 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116915387</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råbockamossen-Ormåsamossarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>459224</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6507509</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Rolf-Göran Carlsson, Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Skogsgruppen Skaraborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>116915391</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råbockamossen-Ormåsamossarna, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>459207</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6507444</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Ada  Arenander, Kurt-Anders Johansson, Liselotte Larsson , Rolf-Göran Carlsson, Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Skogsgruppen Skaraborg</t>
         </is>

--- a/artfynd/A 13365-2024 artfynd.xlsx
+++ b/artfynd/A 13365-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915339</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915340</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915342</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915343</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915346</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915347</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915349</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915351</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915353</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915354</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915387</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915391</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,8 +2457,30 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116915393</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>